--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/03_Öznel Kontrol Yapan Personelin Değerlendirilmesi/EKG-IK-LST-01_oznel_kontrol_operasyonlari_ve_yetkili_personel_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/03_Öznel Kontrol Yapan Personelin Değerlendirilmesi/EKG-IK-LST-01_oznel_kontrol_operasyonlari_ve_yetkili_personel_listesi.xlsx
@@ -830,7 +830,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-LST-01&amp;C&amp;"Arial,Regular"&amp;11Öznel Kontrol Operasyonları ve Yetkili Personel Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Personel yetki listesi nitel test kaydıyla bağlandı; Kappa iddiası ve yanlış payda giderildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1195,7 +1196,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-IK-LST-01&amp;C&amp;"Arial,Regular"&amp;11Öznel Kontrol Operasyonları ve Yetkili Personel Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Personel yetki listesi nitel test kaydıyla bağlandı; Kappa iddiası ve yanlış payda giderildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>